--- a/02.UnityProjects/01.GunfightKing/04. StateMachine/Bot.xlsx
+++ b/02.UnityProjects/01.GunfightKing/04. StateMachine/Bot.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPS\DataSheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\multifps\DataSheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A093D5B8-23C5-47D8-9051-927A5F6F9362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3915" yWindow="2040" windowWidth="23895" windowHeight="13335"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -32,7 +31,7 @@
     <definedName name="ShopType.Kor">Enum!#REF!</definedName>
     <definedName name="StackType.Kor">Enum!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="118">
   <si>
     <t>DB_SOURCE</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -173,10 +172,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>초근접 판단 기준(m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>반응 속도(초)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -198,10 +193,6 @@
   </si>
   <si>
     <t>[50, 50]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[20, 80]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -329,11 +320,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>적을 인지하고 사격까지
-지연 시간(초)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ShootDelayMaxTime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -484,13 +470,63 @@
   </si>
   <si>
     <t>[2,2,2,2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을 인지하고 사격까지
+지연 시간 최댓값(초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을 인지하고 사격까지
+지연 시간 최솟값(초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootDelayImmatureUserMinTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootDelayImmatureUserMaxTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KD 값이 낮은 유저 적을 인지하고
+사격까지 지연 시간 최솟값(초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KD 값이 낮은 유저 적을 인지하고
+사격까지 지연 시간 최댓값(초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[30, 70]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[30, 70]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타겟과 가까워 질때
+정지 거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StopDistance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭탄 설치 시
+초근접 판단 기준(m)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
@@ -955,7 +991,7 @@
         <xdr:cNvPr id="2" name="사각형: 둥근 모서리 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B8502BA-ED26-4D98-8AA7-AC1658758B1F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5B8502BA-ED26-4D98-8AA7-AC1658758B1F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1008,7 +1044,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Database"/>
@@ -1335,8 +1371,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr defaultColWidth="11.75" defaultRowHeight="15.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.75" style="7"/>
@@ -1351,31 +1387,33 @@
     <col min="10" max="10" width="16.75" style="7" customWidth="1"/>
     <col min="11" max="11" width="13.875" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.25" style="7" customWidth="1"/>
-    <col min="13" max="13" width="14.5" style="7" customWidth="1"/>
-    <col min="14" max="14" width="13.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="11.75" style="7"/>
-    <col min="17" max="17" width="17.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="19.75" style="7" customWidth="1"/>
-    <col min="21" max="21" width="41.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.75" style="7" customWidth="1"/>
-    <col min="23" max="23" width="33" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.625" style="29" customWidth="1"/>
-    <col min="25" max="25" width="19.5" style="29" customWidth="1"/>
-    <col min="26" max="26" width="19.875" style="29" customWidth="1"/>
-    <col min="27" max="27" width="16.625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="15" style="29" customWidth="1"/>
-    <col min="29" max="29" width="18.125" style="29" customWidth="1"/>
-    <col min="30" max="30" width="18.25" style="29" customWidth="1"/>
-    <col min="31" max="31" width="13.5" style="7" customWidth="1"/>
-    <col min="32" max="32" width="15.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="11.75" style="7"/>
+    <col min="13" max="14" width="14.5" style="7" customWidth="1"/>
+    <col min="15" max="15" width="13.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.75" style="7"/>
+    <col min="18" max="18" width="17.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="19.75" style="7" customWidth="1"/>
+    <col min="22" max="22" width="32.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="33.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="41.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="41.75" style="7" customWidth="1"/>
+    <col min="26" max="26" width="33" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.625" style="29" customWidth="1"/>
+    <col min="28" max="28" width="19.5" style="29" customWidth="1"/>
+    <col min="29" max="29" width="19.875" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16.625" style="29" customWidth="1"/>
+    <col min="31" max="31" width="15" style="29" customWidth="1"/>
+    <col min="32" max="32" width="18.125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="18.25" style="29" customWidth="1"/>
+    <col min="34" max="34" width="13.5" style="7" customWidth="1"/>
+    <col min="35" max="35" width="15.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="11.75" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="20.25" customHeight="1">
+    <row r="1" spans="1:37" ht="20.25" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1385,10 +1423,10 @@
       <c r="G1" s="10"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:34" ht="15.95" customHeight="1">
+    <row r="2" spans="1:37" ht="15.95" customHeight="1">
       <c r="A2" s="16"/>
       <c r="B2" s="16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="17"/>
@@ -1406,11 +1444,11 @@
       <c r="P2" s="16"/>
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
       <c r="X2" s="16"/>
       <c r="Y2" s="16"/>
       <c r="Z2" s="16"/>
@@ -1422,28 +1460,31 @@
       <c r="AF2" s="16"/>
       <c r="AG2" s="16"/>
       <c r="AH2" s="16"/>
-    </row>
-    <row r="3" spans="1:34" ht="27.75" customHeight="1">
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+    </row>
+    <row r="3" spans="1:37" ht="27.75" customHeight="1">
       <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>21</v>
@@ -1460,94 +1501,103 @@
       <c r="L3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="13" t="s">
+      <c r="R3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" s="30" t="s">
+      <c r="S3" s="13" t="s">
         <v>71</v>
       </c>
       <c r="T3" s="30" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="U3" s="30" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="W3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA3" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB3" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="X3" s="30" t="s">
+      <c r="AC3" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="Y3" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z3" s="30" t="s">
+      <c r="AD3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH3" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="AA3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AI3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ3" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH3" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" ht="15.95" customHeight="1">
+      <c r="AK3" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="15.95" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>105</v>
-      </c>
       <c r="F4" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>18</v>
@@ -1568,90 +1618,99 @@
         <v>29</v>
       </c>
       <c r="N4" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="22" t="s">
+      <c r="P4" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="22" t="s">
-        <v>85</v>
-      </c>
       <c r="Q4" s="22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="R4" s="22" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="S4" s="22" t="s">
         <v>70</v>
       </c>
       <c r="T4" s="22" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U4" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="V4" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="W4" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="X4" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" s="22" t="s">
+      <c r="Z4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA4" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB4" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="X4" s="22" t="s">
+      <c r="AC4" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="Y4" s="22" t="s">
+      <c r="AD4" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB4" s="22" t="s">
+      <c r="AE4" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF4" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="AC4" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD4" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE4" s="22" t="s">
+      <c r="AH4" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI4" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ4" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="AF4" s="22" t="s">
+      <c r="AK4" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="AG4" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH4" s="22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" s="50" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="5" spans="1:37" s="50" customFormat="1" ht="15.95" customHeight="1">
       <c r="A5" s="41">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C5" s="41">
         <v>1</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F5" s="43">
         <v>15</v>
       </c>
       <c r="G5" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="41">
         <v>100</v>
@@ -1663,99 +1722,108 @@
         <v>2</v>
       </c>
       <c r="K5" s="45">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L5" s="45">
         <v>20</v>
       </c>
       <c r="M5" s="46">
+        <v>10</v>
+      </c>
+      <c r="N5" s="45">
+        <v>1</v>
+      </c>
+      <c r="O5" s="46">
+        <v>60</v>
+      </c>
+      <c r="P5" s="46">
+        <v>80</v>
+      </c>
+      <c r="Q5" s="45">
+        <v>1.3</v>
+      </c>
+      <c r="R5" s="46">
         <v>30</v>
       </c>
-      <c r="N5" s="46">
-        <v>60</v>
-      </c>
-      <c r="O5" s="46">
-        <v>80</v>
-      </c>
-      <c r="P5" s="45">
+      <c r="S5" s="46">
+        <v>1</v>
+      </c>
+      <c r="T5" s="45">
         <v>1.3</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="U5" s="45">
+        <v>1.6</v>
+      </c>
+      <c r="V5" s="45">
+        <v>2.5</v>
+      </c>
+      <c r="W5" s="45">
+        <v>4</v>
+      </c>
+      <c r="X5" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y5" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z5" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA5" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB5" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC5" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD5" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="48">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="49">
+        <v>65</v>
+      </c>
+      <c r="AI5" s="49">
         <v>30</v>
       </c>
-      <c r="R5" s="46">
-        <v>1</v>
-      </c>
-      <c r="S5" s="45">
-        <v>1.3</v>
-      </c>
-      <c r="T5" s="45">
-        <v>1.6</v>
-      </c>
-      <c r="U5" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W5" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y5" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z5" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA5" s="48">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="48">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="48">
+      <c r="AJ5" s="49">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="49">
         <v>0</v>
       </c>
-      <c r="AE5" s="49">
-        <v>65</v>
-      </c>
-      <c r="AF5" s="49">
-        <v>30</v>
-      </c>
-      <c r="AG5" s="49">
-        <v>5</v>
-      </c>
-      <c r="AH5" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" s="50" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="6" spans="1:37" s="50" customFormat="1" ht="15.95" customHeight="1">
       <c r="A6" s="41">
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="41">
         <v>1</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F6" s="43">
         <v>15</v>
       </c>
       <c r="G6" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="41">
         <v>100</v>
@@ -1767,99 +1835,108 @@
         <v>2</v>
       </c>
       <c r="K6" s="45">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="45">
         <v>20</v>
       </c>
       <c r="M6" s="46">
+        <v>10</v>
+      </c>
+      <c r="N6" s="45">
+        <v>1</v>
+      </c>
+      <c r="O6" s="46">
+        <v>60</v>
+      </c>
+      <c r="P6" s="46">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="45">
+        <v>1.3</v>
+      </c>
+      <c r="R6" s="46">
         <v>30</v>
       </c>
-      <c r="N6" s="46">
-        <v>60</v>
-      </c>
-      <c r="O6" s="46">
-        <v>80</v>
-      </c>
-      <c r="P6" s="45">
+      <c r="S6" s="46">
+        <v>1</v>
+      </c>
+      <c r="T6" s="45">
         <v>1.3</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="U6" s="45">
+        <v>1.6</v>
+      </c>
+      <c r="V6" s="45">
+        <v>2.5</v>
+      </c>
+      <c r="W6" s="45">
+        <v>4</v>
+      </c>
+      <c r="X6" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y6" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z6" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA6" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB6" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC6" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD6" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="48">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="49">
+        <v>65</v>
+      </c>
+      <c r="AI6" s="49">
         <v>30</v>
       </c>
-      <c r="R6" s="46">
-        <v>1</v>
-      </c>
-      <c r="S6" s="45">
-        <v>1.3</v>
-      </c>
-      <c r="T6" s="45">
-        <v>1.6</v>
-      </c>
-      <c r="U6" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="V6" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W6" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="X6" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y6" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z6" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA6" s="48">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="48">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="48">
+      <c r="AJ6" s="49">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="49">
         <v>0</v>
       </c>
-      <c r="AE6" s="49">
-        <v>65</v>
-      </c>
-      <c r="AF6" s="49">
-        <v>30</v>
-      </c>
-      <c r="AG6" s="49">
-        <v>5</v>
-      </c>
-      <c r="AH6" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" s="50" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="7" spans="1:37" s="50" customFormat="1" ht="15.95" customHeight="1">
       <c r="A7" s="41">
         <v>3</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C7" s="41">
         <v>1</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F7" s="43">
         <v>15</v>
       </c>
       <c r="G7" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="41">
         <v>100</v>
@@ -1871,93 +1948,102 @@
         <v>2</v>
       </c>
       <c r="K7" s="45">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L7" s="45">
         <v>20</v>
       </c>
       <c r="M7" s="46">
+        <v>10</v>
+      </c>
+      <c r="N7" s="45">
+        <v>1</v>
+      </c>
+      <c r="O7" s="46">
+        <v>60</v>
+      </c>
+      <c r="P7" s="46">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="45">
+        <v>1.3</v>
+      </c>
+      <c r="R7" s="46">
         <v>30</v>
       </c>
-      <c r="N7" s="46">
-        <v>60</v>
-      </c>
-      <c r="O7" s="46">
-        <v>80</v>
-      </c>
-      <c r="P7" s="45">
+      <c r="S7" s="46">
+        <v>1</v>
+      </c>
+      <c r="T7" s="45">
         <v>1.3</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="U7" s="45">
+        <v>1.6</v>
+      </c>
+      <c r="V7" s="45">
+        <v>2.5</v>
+      </c>
+      <c r="W7" s="45">
+        <v>4</v>
+      </c>
+      <c r="X7" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y7" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z7" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA7" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD7" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="48">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="49">
+        <v>65</v>
+      </c>
+      <c r="AI7" s="49">
         <v>30</v>
       </c>
-      <c r="R7" s="46">
-        <v>1</v>
-      </c>
-      <c r="S7" s="45">
-        <v>1.3</v>
-      </c>
-      <c r="T7" s="45">
-        <v>1.6</v>
-      </c>
-      <c r="U7" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="V7" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W7" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="X7" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y7" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z7" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA7" s="48">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="48">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="48">
+      <c r="AJ7" s="49">
+        <v>5</v>
+      </c>
+      <c r="AK7" s="49">
         <v>0</v>
       </c>
-      <c r="AE7" s="49">
-        <v>65</v>
-      </c>
-      <c r="AF7" s="49">
-        <v>30</v>
-      </c>
-      <c r="AG7" s="49">
-        <v>5</v>
-      </c>
-      <c r="AH7" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="8" spans="1:37" ht="15.95" customHeight="1">
       <c r="A8" s="31">
         <v>4</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8" s="11">
         <v>15</v>
@@ -1975,93 +2061,102 @@
         <v>2</v>
       </c>
       <c r="K8" s="25">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L8" s="24">
         <v>20</v>
       </c>
       <c r="M8" s="27">
+        <v>10</v>
+      </c>
+      <c r="N8" s="24">
+        <v>1</v>
+      </c>
+      <c r="O8" s="26">
+        <v>60</v>
+      </c>
+      <c r="P8" s="27">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>1</v>
+      </c>
+      <c r="R8" s="27">
         <v>30</v>
       </c>
-      <c r="N8" s="26">
-        <v>60</v>
-      </c>
-      <c r="O8" s="27">
-        <v>90</v>
-      </c>
-      <c r="P8" s="25">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="27">
+      <c r="S8" s="27">
+        <v>1</v>
+      </c>
+      <c r="T8" s="24">
+        <v>1</v>
+      </c>
+      <c r="U8" s="24">
+        <v>1.2</v>
+      </c>
+      <c r="V8" s="24">
+        <v>1.5</v>
+      </c>
+      <c r="W8" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z8" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA8" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB8" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC8" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD8" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="38">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="38">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="39">
+        <v>65</v>
+      </c>
+      <c r="AI8" s="39">
         <v>30</v>
       </c>
-      <c r="R8" s="27">
-        <v>1</v>
-      </c>
-      <c r="S8" s="24">
-        <v>1</v>
-      </c>
-      <c r="T8" s="24">
-        <v>1.2</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W8" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y8" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z8" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA8" s="38">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="38">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="38">
+      <c r="AJ8" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="39">
         <v>0</v>
       </c>
-      <c r="AE8" s="39">
-        <v>65</v>
-      </c>
-      <c r="AF8" s="39">
-        <v>30</v>
-      </c>
-      <c r="AG8" s="39">
-        <v>5</v>
-      </c>
-      <c r="AH8" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="9" spans="1:37" ht="15.95" customHeight="1">
       <c r="A9" s="31">
         <v>5</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F9" s="11">
         <v>15</v>
@@ -2079,93 +2174,102 @@
         <v>2</v>
       </c>
       <c r="K9" s="25">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L9" s="24">
         <v>20</v>
       </c>
       <c r="M9" s="27">
+        <v>10</v>
+      </c>
+      <c r="N9" s="24">
+        <v>1</v>
+      </c>
+      <c r="O9" s="26">
+        <v>60</v>
+      </c>
+      <c r="P9" s="27">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>1</v>
+      </c>
+      <c r="R9" s="27">
         <v>30</v>
       </c>
-      <c r="N9" s="26">
-        <v>60</v>
-      </c>
-      <c r="O9" s="27">
-        <v>90</v>
-      </c>
-      <c r="P9" s="25">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="27">
+      <c r="S9" s="27">
+        <v>1</v>
+      </c>
+      <c r="T9" s="24">
+        <v>1</v>
+      </c>
+      <c r="U9" s="24">
+        <v>1.2</v>
+      </c>
+      <c r="V9" s="24">
+        <v>1.5</v>
+      </c>
+      <c r="W9" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z9" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA9" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB9" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC9" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="39">
+        <v>65</v>
+      </c>
+      <c r="AI9" s="39">
         <v>30</v>
       </c>
-      <c r="R9" s="27">
-        <v>1</v>
-      </c>
-      <c r="S9" s="24">
-        <v>1</v>
-      </c>
-      <c r="T9" s="24">
-        <v>1.2</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W9" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X9" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y9" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z9" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA9" s="38">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="38">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="38">
+      <c r="AJ9" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="39">
         <v>0</v>
       </c>
-      <c r="AE9" s="39">
-        <v>65</v>
-      </c>
-      <c r="AF9" s="39">
-        <v>30</v>
-      </c>
-      <c r="AG9" s="39">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="10" spans="1:37" ht="15.95" customHeight="1">
       <c r="A10" s="31">
         <v>6</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F10" s="11">
         <v>15</v>
@@ -2183,93 +2287,102 @@
         <v>2</v>
       </c>
       <c r="K10" s="25">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L10" s="24">
         <v>20</v>
       </c>
       <c r="M10" s="27">
+        <v>10</v>
+      </c>
+      <c r="N10" s="24">
+        <v>1</v>
+      </c>
+      <c r="O10" s="26">
+        <v>60</v>
+      </c>
+      <c r="P10" s="27">
+        <v>90</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>1</v>
+      </c>
+      <c r="R10" s="27">
         <v>30</v>
       </c>
-      <c r="N10" s="26">
-        <v>60</v>
-      </c>
-      <c r="O10" s="27">
-        <v>90</v>
-      </c>
-      <c r="P10" s="25">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="27">
+      <c r="S10" s="27">
+        <v>1</v>
+      </c>
+      <c r="T10" s="24">
+        <v>1</v>
+      </c>
+      <c r="U10" s="24">
+        <v>1.2</v>
+      </c>
+      <c r="V10" s="24">
+        <v>1.5</v>
+      </c>
+      <c r="W10" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="X10" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z10" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA10" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB10" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC10" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD10" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="38">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="38">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="39">
+        <v>65</v>
+      </c>
+      <c r="AI10" s="39">
         <v>30</v>
       </c>
-      <c r="R10" s="27">
-        <v>1</v>
-      </c>
-      <c r="S10" s="24">
-        <v>1</v>
-      </c>
-      <c r="T10" s="24">
-        <v>1.2</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W10" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y10" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z10" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA10" s="38">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="38">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="38">
+      <c r="AJ10" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="39">
         <v>0</v>
       </c>
-      <c r="AE10" s="39">
-        <v>65</v>
-      </c>
-      <c r="AF10" s="39">
-        <v>30</v>
-      </c>
-      <c r="AG10" s="39">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" s="60" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="11" spans="1:37" s="60" customFormat="1" ht="15.95" customHeight="1">
       <c r="A11" s="51">
         <v>7</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F11" s="53">
         <v>15</v>
@@ -2287,93 +2400,102 @@
         <v>2</v>
       </c>
       <c r="K11" s="55">
-        <v>4.5</v>
+        <v>6.45</v>
       </c>
       <c r="L11" s="55">
         <v>20</v>
       </c>
       <c r="M11" s="56">
+        <v>10</v>
+      </c>
+      <c r="N11" s="55">
+        <v>1</v>
+      </c>
+      <c r="O11" s="56">
+        <v>60</v>
+      </c>
+      <c r="P11" s="56">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="55">
+        <v>0.6</v>
+      </c>
+      <c r="R11" s="56">
         <v>30</v>
       </c>
-      <c r="N11" s="56">
-        <v>60</v>
-      </c>
-      <c r="O11" s="56">
-        <v>100</v>
-      </c>
-      <c r="P11" s="55">
+      <c r="S11" s="56">
+        <v>1</v>
+      </c>
+      <c r="T11" s="55">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="56">
+      <c r="U11" s="55">
+        <v>0.9</v>
+      </c>
+      <c r="V11" s="55">
+        <v>1</v>
+      </c>
+      <c r="W11" s="55">
+        <v>1.5</v>
+      </c>
+      <c r="X11" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y11" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z11" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA11" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB11" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC11" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD11" s="58">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="58">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="58">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="59">
+        <v>65</v>
+      </c>
+      <c r="AI11" s="59">
         <v>30</v>
       </c>
-      <c r="R11" s="56">
-        <v>1</v>
-      </c>
-      <c r="S11" s="55">
-        <v>0.6</v>
-      </c>
-      <c r="T11" s="55">
-        <v>0.9</v>
-      </c>
-      <c r="U11" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="V11" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W11" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="X11" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y11" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z11" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA11" s="58">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="58">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="58">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="58">
+      <c r="AJ11" s="59">
+        <v>5</v>
+      </c>
+      <c r="AK11" s="59">
         <v>0</v>
       </c>
-      <c r="AE11" s="59">
-        <v>65</v>
-      </c>
-      <c r="AF11" s="59">
-        <v>30</v>
-      </c>
-      <c r="AG11" s="59">
-        <v>5</v>
-      </c>
-      <c r="AH11" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" s="60" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="12" spans="1:37" s="60" customFormat="1" ht="15.95" customHeight="1">
       <c r="A12" s="51">
         <v>8</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F12" s="53">
         <v>15</v>
@@ -2391,93 +2513,102 @@
         <v>2</v>
       </c>
       <c r="K12" s="55">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L12" s="55">
         <v>20</v>
       </c>
       <c r="M12" s="56">
+        <v>10</v>
+      </c>
+      <c r="N12" s="55">
+        <v>1</v>
+      </c>
+      <c r="O12" s="56">
+        <v>60</v>
+      </c>
+      <c r="P12" s="56">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="55">
+        <v>0.6</v>
+      </c>
+      <c r="R12" s="56">
         <v>30</v>
       </c>
-      <c r="N12" s="56">
-        <v>60</v>
-      </c>
-      <c r="O12" s="56">
-        <v>100</v>
-      </c>
-      <c r="P12" s="55">
+      <c r="S12" s="56">
+        <v>1</v>
+      </c>
+      <c r="T12" s="55">
         <v>0.6</v>
       </c>
-      <c r="Q12" s="56">
+      <c r="U12" s="55">
+        <v>0.9</v>
+      </c>
+      <c r="V12" s="55">
+        <v>1</v>
+      </c>
+      <c r="W12" s="55">
+        <v>1.5</v>
+      </c>
+      <c r="X12" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y12" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z12" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA12" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB12" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC12" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD12" s="58">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="58">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="58">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="59">
+        <v>65</v>
+      </c>
+      <c r="AI12" s="59">
         <v>30</v>
       </c>
-      <c r="R12" s="56">
-        <v>1</v>
-      </c>
-      <c r="S12" s="55">
-        <v>0.6</v>
-      </c>
-      <c r="T12" s="55">
-        <v>0.9</v>
-      </c>
-      <c r="U12" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="V12" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W12" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="X12" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y12" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z12" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA12" s="58">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="58">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="58">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="58">
+      <c r="AJ12" s="59">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="59">
         <v>0</v>
       </c>
-      <c r="AE12" s="59">
-        <v>65</v>
-      </c>
-      <c r="AF12" s="59">
-        <v>30</v>
-      </c>
-      <c r="AG12" s="59">
-        <v>5</v>
-      </c>
-      <c r="AH12" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" s="60" customFormat="1" ht="15.95" customHeight="1">
+    </row>
+    <row r="13" spans="1:37" s="60" customFormat="1" ht="15.95" customHeight="1">
       <c r="A13" s="51">
         <v>9</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F13" s="53">
         <v>15</v>
@@ -2495,99 +2626,108 @@
         <v>2</v>
       </c>
       <c r="K13" s="55">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L13" s="55">
         <v>20</v>
       </c>
       <c r="M13" s="56">
+        <v>10</v>
+      </c>
+      <c r="N13" s="55">
+        <v>1</v>
+      </c>
+      <c r="O13" s="56">
+        <v>60</v>
+      </c>
+      <c r="P13" s="56">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="55">
+        <v>0.6</v>
+      </c>
+      <c r="R13" s="56">
         <v>30</v>
       </c>
-      <c r="N13" s="56">
-        <v>60</v>
-      </c>
-      <c r="O13" s="56">
-        <v>100</v>
-      </c>
-      <c r="P13" s="55">
+      <c r="S13" s="56">
+        <v>1</v>
+      </c>
+      <c r="T13" s="55">
         <v>0.6</v>
       </c>
-      <c r="Q13" s="56">
+      <c r="U13" s="55">
+        <v>0.9</v>
+      </c>
+      <c r="V13" s="55">
+        <v>1</v>
+      </c>
+      <c r="W13" s="55">
+        <v>1.5</v>
+      </c>
+      <c r="X13" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y13" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z13" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA13" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB13" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC13" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD13" s="58">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="58">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="58">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="59">
+        <v>65</v>
+      </c>
+      <c r="AI13" s="59">
         <v>30</v>
       </c>
-      <c r="R13" s="56">
-        <v>1</v>
-      </c>
-      <c r="S13" s="55">
-        <v>0.6</v>
-      </c>
-      <c r="T13" s="55">
-        <v>0.9</v>
-      </c>
-      <c r="U13" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="V13" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W13" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="X13" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y13" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z13" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA13" s="58">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="58">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="58">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="58">
+      <c r="AJ13" s="59">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="59">
         <v>0</v>
       </c>
-      <c r="AE13" s="59">
-        <v>65</v>
-      </c>
-      <c r="AF13" s="59">
-        <v>30</v>
-      </c>
-      <c r="AG13" s="59">
-        <v>5</v>
-      </c>
-      <c r="AH13" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="14" spans="1:37" ht="15.95" customHeight="1">
       <c r="A14" s="41">
         <v>10</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F14" s="43">
         <v>15</v>
       </c>
       <c r="G14" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="41">
         <v>100</v>
@@ -2599,99 +2739,108 @@
         <v>2</v>
       </c>
       <c r="K14" s="45">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="L14" s="45">
         <v>20</v>
       </c>
       <c r="M14" s="46">
+        <v>10</v>
+      </c>
+      <c r="N14" s="45">
+        <v>1</v>
+      </c>
+      <c r="O14" s="46">
+        <v>60</v>
+      </c>
+      <c r="P14" s="46">
+        <v>80</v>
+      </c>
+      <c r="Q14" s="45">
+        <v>2.5</v>
+      </c>
+      <c r="R14" s="46">
         <v>30</v>
       </c>
-      <c r="N14" s="46">
-        <v>60</v>
-      </c>
-      <c r="O14" s="46">
-        <v>80</v>
-      </c>
-      <c r="P14" s="45">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" s="46">
-        <v>30</v>
-      </c>
-      <c r="R14" s="46">
-        <v>1</v>
-      </c>
-      <c r="S14" s="45">
-        <v>2.5</v>
+      <c r="S14" s="46">
+        <v>1</v>
       </c>
       <c r="T14" s="45">
         <v>3</v>
       </c>
-      <c r="U14" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="V14" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W14" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="X14" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y14" s="47" t="s">
-        <v>59</v>
+      <c r="U14" s="45">
+        <v>5</v>
+      </c>
+      <c r="V14" s="45">
+        <v>3</v>
+      </c>
+      <c r="W14" s="45">
+        <v>5</v>
+      </c>
+      <c r="X14" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y14" s="41" t="s">
+        <v>38</v>
       </c>
       <c r="Z14" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA14" s="48">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="48">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="AA14" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB14" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC14" s="47" t="s">
+        <v>57</v>
       </c>
       <c r="AD14" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="48">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="48">
         <v>0</v>
       </c>
-      <c r="AE14" s="49">
+      <c r="AH14" s="49">
         <v>65</v>
       </c>
-      <c r="AF14" s="49">
+      <c r="AI14" s="49">
         <v>30</v>
       </c>
-      <c r="AG14" s="49">
+      <c r="AJ14" s="49">
         <v>5</v>
       </c>
-      <c r="AH14" s="49">
+      <c r="AK14" s="49">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="15.95" customHeight="1">
+    <row r="15" spans="1:37" ht="15.95" customHeight="1">
       <c r="A15" s="41">
         <v>11</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F15" s="43">
         <v>15</v>
       </c>
       <c r="G15" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="41">
         <v>100</v>
@@ -2703,99 +2852,108 @@
         <v>2</v>
       </c>
       <c r="K15" s="45">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="L15" s="45">
         <v>20</v>
       </c>
       <c r="M15" s="46">
+        <v>10</v>
+      </c>
+      <c r="N15" s="45">
+        <v>1</v>
+      </c>
+      <c r="O15" s="46">
+        <v>60</v>
+      </c>
+      <c r="P15" s="46">
+        <v>80</v>
+      </c>
+      <c r="Q15" s="45">
+        <v>2.5</v>
+      </c>
+      <c r="R15" s="46">
         <v>30</v>
       </c>
-      <c r="N15" s="46">
-        <v>60</v>
-      </c>
-      <c r="O15" s="46">
-        <v>80</v>
-      </c>
-      <c r="P15" s="45">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" s="46">
-        <v>30</v>
-      </c>
-      <c r="R15" s="46">
-        <v>1</v>
-      </c>
-      <c r="S15" s="45">
-        <v>2.5</v>
+      <c r="S15" s="46">
+        <v>1</v>
       </c>
       <c r="T15" s="45">
         <v>3</v>
       </c>
-      <c r="U15" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="V15" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W15" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="X15" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y15" s="47" t="s">
-        <v>59</v>
+      <c r="U15" s="45">
+        <v>5</v>
+      </c>
+      <c r="V15" s="45">
+        <v>3</v>
+      </c>
+      <c r="W15" s="45">
+        <v>5</v>
+      </c>
+      <c r="X15" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y15" s="41" t="s">
+        <v>38</v>
       </c>
       <c r="Z15" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA15" s="48">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="48">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="AA15" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC15" s="47" t="s">
+        <v>57</v>
       </c>
       <c r="AD15" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="48">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="48">
         <v>0</v>
       </c>
-      <c r="AE15" s="49">
+      <c r="AH15" s="49">
         <v>65</v>
       </c>
-      <c r="AF15" s="49">
+      <c r="AI15" s="49">
         <v>30</v>
       </c>
-      <c r="AG15" s="49">
+      <c r="AJ15" s="49">
         <v>5</v>
       </c>
-      <c r="AH15" s="49">
+      <c r="AK15" s="49">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15.95" customHeight="1">
+    <row r="16" spans="1:37" ht="15.95" customHeight="1">
       <c r="A16" s="41">
         <v>12</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F16" s="43">
         <v>15</v>
       </c>
       <c r="G16" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="41">
         <v>100</v>
@@ -2807,93 +2965,102 @@
         <v>2</v>
       </c>
       <c r="K16" s="45">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="L16" s="45">
         <v>20</v>
       </c>
       <c r="M16" s="46">
+        <v>10</v>
+      </c>
+      <c r="N16" s="45">
+        <v>1</v>
+      </c>
+      <c r="O16" s="46">
+        <v>60</v>
+      </c>
+      <c r="P16" s="46">
+        <v>80</v>
+      </c>
+      <c r="Q16" s="45">
+        <v>2.5</v>
+      </c>
+      <c r="R16" s="46">
         <v>30</v>
       </c>
-      <c r="N16" s="46">
-        <v>60</v>
-      </c>
-      <c r="O16" s="46">
-        <v>80</v>
-      </c>
-      <c r="P16" s="45">
-        <v>2.5</v>
-      </c>
-      <c r="Q16" s="46">
-        <v>30</v>
-      </c>
-      <c r="R16" s="46">
-        <v>1</v>
-      </c>
-      <c r="S16" s="45">
-        <v>2.5</v>
+      <c r="S16" s="46">
+        <v>1</v>
       </c>
       <c r="T16" s="45">
         <v>3</v>
       </c>
-      <c r="U16" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="V16" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W16" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="X16" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y16" s="47" t="s">
-        <v>59</v>
+      <c r="U16" s="45">
+        <v>5</v>
+      </c>
+      <c r="V16" s="45">
+        <v>3</v>
+      </c>
+      <c r="W16" s="45">
+        <v>5</v>
+      </c>
+      <c r="X16" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y16" s="41" t="s">
+        <v>38</v>
       </c>
       <c r="Z16" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="48">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="AA16" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB16" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC16" s="47" t="s">
+        <v>57</v>
       </c>
       <c r="AD16" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="48">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="48">
         <v>0</v>
       </c>
-      <c r="AE16" s="49">
+      <c r="AH16" s="49">
         <v>65</v>
       </c>
-      <c r="AF16" s="49">
+      <c r="AI16" s="49">
         <v>30</v>
       </c>
-      <c r="AG16" s="49">
+      <c r="AJ16" s="49">
         <v>5</v>
       </c>
-      <c r="AH16" s="49">
+      <c r="AK16" s="49">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="15.95" customHeight="1">
+    <row r="17" spans="1:37" ht="15.95" customHeight="1">
       <c r="A17" s="31">
         <v>13</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F17" s="11">
         <v>15</v>
@@ -2911,93 +3078,102 @@
         <v>2</v>
       </c>
       <c r="K17" s="25">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L17" s="24">
         <v>20</v>
       </c>
       <c r="M17" s="27">
+        <v>10</v>
+      </c>
+      <c r="N17" s="24">
+        <v>1</v>
+      </c>
+      <c r="O17" s="26">
+        <v>60</v>
+      </c>
+      <c r="P17" s="27">
+        <v>90</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="R17" s="27">
         <v>30</v>
       </c>
-      <c r="N17" s="26">
-        <v>60</v>
-      </c>
-      <c r="O17" s="27">
-        <v>90</v>
-      </c>
-      <c r="P17" s="25">
+      <c r="S17" s="27">
+        <v>1</v>
+      </c>
+      <c r="T17" s="24">
         <v>1.5</v>
       </c>
-      <c r="Q17" s="27">
+      <c r="U17" s="24">
+        <v>2</v>
+      </c>
+      <c r="V17" s="24">
+        <v>1.5</v>
+      </c>
+      <c r="W17" s="24">
+        <v>2</v>
+      </c>
+      <c r="X17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z17" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA17" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD17" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="38">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="38">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="39">
+        <v>65</v>
+      </c>
+      <c r="AI17" s="39">
         <v>30</v>
       </c>
-      <c r="R17" s="27">
-        <v>1</v>
-      </c>
-      <c r="S17" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="T17" s="24">
-        <v>2</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W17" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X17" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y17" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z17" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA17" s="38">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="38">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="38">
+      <c r="AJ17" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="39">
         <v>0</v>
       </c>
-      <c r="AE17" s="39">
-        <v>65</v>
-      </c>
-      <c r="AF17" s="39">
-        <v>30</v>
-      </c>
-      <c r="AG17" s="39">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="18" spans="1:37" ht="15.95" customHeight="1">
       <c r="A18" s="31">
         <v>14</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F18" s="11">
         <v>15</v>
@@ -3015,93 +3191,102 @@
         <v>2</v>
       </c>
       <c r="K18" s="25">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L18" s="24">
         <v>20</v>
       </c>
       <c r="M18" s="27">
+        <v>10</v>
+      </c>
+      <c r="N18" s="24">
+        <v>1</v>
+      </c>
+      <c r="O18" s="26">
+        <v>60</v>
+      </c>
+      <c r="P18" s="27">
+        <v>90</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="R18" s="27">
         <v>30</v>
       </c>
-      <c r="N18" s="26">
-        <v>60</v>
-      </c>
-      <c r="O18" s="27">
-        <v>90</v>
-      </c>
-      <c r="P18" s="25">
+      <c r="S18" s="27">
+        <v>1</v>
+      </c>
+      <c r="T18" s="24">
         <v>1.5</v>
       </c>
-      <c r="Q18" s="27">
+      <c r="U18" s="24">
+        <v>2</v>
+      </c>
+      <c r="V18" s="24">
+        <v>1.5</v>
+      </c>
+      <c r="W18" s="24">
+        <v>2</v>
+      </c>
+      <c r="X18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z18" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA18" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD18" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="38">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="38">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="39">
+        <v>65</v>
+      </c>
+      <c r="AI18" s="39">
         <v>30</v>
       </c>
-      <c r="R18" s="27">
-        <v>1</v>
-      </c>
-      <c r="S18" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="T18" s="24">
-        <v>2</v>
-      </c>
-      <c r="U18" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V18" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W18" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X18" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y18" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z18" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA18" s="38">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="38">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="38">
+      <c r="AJ18" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="39">
         <v>0</v>
       </c>
-      <c r="AE18" s="39">
-        <v>65</v>
-      </c>
-      <c r="AF18" s="39">
-        <v>30</v>
-      </c>
-      <c r="AG18" s="39">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="19" spans="1:37" ht="15.95" customHeight="1">
       <c r="A19" s="31">
         <v>15</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F19" s="11">
         <v>15</v>
@@ -3119,93 +3304,102 @@
         <v>2</v>
       </c>
       <c r="K19" s="25">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L19" s="24">
         <v>20</v>
       </c>
       <c r="M19" s="27">
+        <v>10</v>
+      </c>
+      <c r="N19" s="24">
+        <v>1</v>
+      </c>
+      <c r="O19" s="26">
+        <v>60</v>
+      </c>
+      <c r="P19" s="27">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="R19" s="27">
         <v>30</v>
       </c>
-      <c r="N19" s="26">
-        <v>60</v>
-      </c>
-      <c r="O19" s="27">
-        <v>90</v>
-      </c>
-      <c r="P19" s="25">
+      <c r="S19" s="27">
+        <v>1</v>
+      </c>
+      <c r="T19" s="24">
         <v>1.5</v>
       </c>
-      <c r="Q19" s="27">
+      <c r="U19" s="24">
+        <v>2</v>
+      </c>
+      <c r="V19" s="24">
+        <v>1.5</v>
+      </c>
+      <c r="W19" s="24">
+        <v>2</v>
+      </c>
+      <c r="X19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z19" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA19" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB19" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC19" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD19" s="38">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="38">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="38">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="39">
+        <v>65</v>
+      </c>
+      <c r="AI19" s="39">
         <v>30</v>
       </c>
-      <c r="R19" s="27">
-        <v>1</v>
-      </c>
-      <c r="S19" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="T19" s="24">
-        <v>2</v>
-      </c>
-      <c r="U19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W19" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X19" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y19" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z19" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA19" s="38">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="38">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="38">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="38">
+      <c r="AJ19" s="39">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="39">
         <v>0</v>
       </c>
-      <c r="AE19" s="39">
-        <v>65</v>
-      </c>
-      <c r="AF19" s="39">
-        <v>30</v>
-      </c>
-      <c r="AG19" s="39">
-        <v>5</v>
-      </c>
-      <c r="AH19" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="20" spans="1:37" ht="15.95" customHeight="1">
       <c r="A20" s="51">
         <v>16</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F20" s="53">
         <v>15</v>
@@ -3223,93 +3417,102 @@
         <v>2</v>
       </c>
       <c r="K20" s="55">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L20" s="55">
         <v>20</v>
       </c>
       <c r="M20" s="56">
+        <v>10</v>
+      </c>
+      <c r="N20" s="55">
+        <v>1</v>
+      </c>
+      <c r="O20" s="56">
+        <v>60</v>
+      </c>
+      <c r="P20" s="56">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="R20" s="56">
         <v>30</v>
       </c>
-      <c r="N20" s="56">
-        <v>60</v>
-      </c>
-      <c r="O20" s="56">
-        <v>100</v>
-      </c>
-      <c r="P20" s="55">
+      <c r="S20" s="56">
+        <v>1</v>
+      </c>
+      <c r="T20" s="55">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="56">
+      <c r="U20" s="55">
+        <v>0.8</v>
+      </c>
+      <c r="V20" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="W20" s="55">
+        <v>0.8</v>
+      </c>
+      <c r="X20" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y20" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z20" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA20" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB20" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC20" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD20" s="58">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="58">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="58">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="59">
+        <v>65</v>
+      </c>
+      <c r="AI20" s="59">
         <v>30</v>
       </c>
-      <c r="R20" s="56">
-        <v>1</v>
-      </c>
-      <c r="S20" s="55">
-        <v>0.4</v>
-      </c>
-      <c r="T20" s="55">
-        <v>0.8</v>
-      </c>
-      <c r="U20" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="V20" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W20" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="X20" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y20" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z20" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA20" s="58">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="58">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="58">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="58">
+      <c r="AJ20" s="59">
+        <v>5</v>
+      </c>
+      <c r="AK20" s="59">
         <v>0</v>
       </c>
-      <c r="AE20" s="59">
-        <v>65</v>
-      </c>
-      <c r="AF20" s="59">
-        <v>30</v>
-      </c>
-      <c r="AG20" s="59">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="21" spans="1:37" ht="15.95" customHeight="1">
       <c r="A21" s="51">
         <v>17</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F21" s="53">
         <v>15</v>
@@ -3327,93 +3530,102 @@
         <v>2</v>
       </c>
       <c r="K21" s="55">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L21" s="55">
         <v>20</v>
       </c>
       <c r="M21" s="56">
+        <v>10</v>
+      </c>
+      <c r="N21" s="55">
+        <v>1</v>
+      </c>
+      <c r="O21" s="56">
+        <v>60</v>
+      </c>
+      <c r="P21" s="56">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="R21" s="56">
         <v>30</v>
       </c>
-      <c r="N21" s="56">
-        <v>60</v>
-      </c>
-      <c r="O21" s="56">
-        <v>100</v>
-      </c>
-      <c r="P21" s="55">
+      <c r="S21" s="56">
+        <v>1</v>
+      </c>
+      <c r="T21" s="55">
         <v>0.4</v>
       </c>
-      <c r="Q21" s="56">
+      <c r="U21" s="55">
+        <v>0.8</v>
+      </c>
+      <c r="V21" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="W21" s="55">
+        <v>0.8</v>
+      </c>
+      <c r="X21" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y21" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z21" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA21" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB21" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC21" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD21" s="58">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="58">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="58">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="59">
+        <v>65</v>
+      </c>
+      <c r="AI21" s="59">
         <v>30</v>
       </c>
-      <c r="R21" s="56">
-        <v>1</v>
-      </c>
-      <c r="S21" s="55">
-        <v>0.4</v>
-      </c>
-      <c r="T21" s="55">
-        <v>0.8</v>
-      </c>
-      <c r="U21" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="V21" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W21" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="X21" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y21" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z21" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA21" s="58">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="58">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="58">
-        <v>1</v>
-      </c>
-      <c r="AD21" s="58">
+      <c r="AJ21" s="59">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="59">
         <v>0</v>
       </c>
-      <c r="AE21" s="59">
-        <v>65</v>
-      </c>
-      <c r="AF21" s="59">
-        <v>30</v>
-      </c>
-      <c r="AG21" s="59">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:34" ht="15.95" customHeight="1">
+    </row>
+    <row r="22" spans="1:37" ht="15.95" customHeight="1">
       <c r="A22" s="51">
         <v>18</v>
       </c>
       <c r="B22" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F22" s="53">
         <v>15</v>
@@ -3431,75 +3643,84 @@
         <v>2</v>
       </c>
       <c r="K22" s="55">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="L22" s="55">
         <v>20</v>
       </c>
       <c r="M22" s="56">
+        <v>10</v>
+      </c>
+      <c r="N22" s="55">
+        <v>1</v>
+      </c>
+      <c r="O22" s="56">
+        <v>60</v>
+      </c>
+      <c r="P22" s="56">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="R22" s="56">
         <v>30</v>
       </c>
-      <c r="N22" s="56">
-        <v>60</v>
-      </c>
-      <c r="O22" s="56">
-        <v>100</v>
-      </c>
-      <c r="P22" s="55">
+      <c r="S22" s="56">
+        <v>1</v>
+      </c>
+      <c r="T22" s="55">
         <v>0.4</v>
       </c>
-      <c r="Q22" s="56">
+      <c r="U22" s="55">
+        <v>0.8</v>
+      </c>
+      <c r="V22" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="W22" s="55">
+        <v>0.8</v>
+      </c>
+      <c r="X22" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y22" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z22" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA22" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB22" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC22" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD22" s="58">
+        <v>1</v>
+      </c>
+      <c r="AE22" s="58">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="58">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="59">
+        <v>65</v>
+      </c>
+      <c r="AI22" s="59">
         <v>30</v>
       </c>
-      <c r="R22" s="56">
-        <v>1</v>
-      </c>
-      <c r="S22" s="55">
-        <v>0.4</v>
-      </c>
-      <c r="T22" s="55">
-        <v>0.8</v>
-      </c>
-      <c r="U22" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="V22" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W22" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="X22" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y22" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z22" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA22" s="58">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="58">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="58">
-        <v>1</v>
-      </c>
-      <c r="AD22" s="58">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="59">
-        <v>65</v>
-      </c>
-      <c r="AF22" s="59">
-        <v>30</v>
-      </c>
-      <c r="AG22" s="59">
+      <c r="AJ22" s="59">
         <v>5</v>
       </c>
-      <c r="AH22" s="59">
+      <c r="AK22" s="59">
         <v>0</v>
       </c>
     </row>
@@ -3510,7 +3731,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Enum!$C$3:$C$5</xm:f>
           </x14:formula1>
@@ -3523,7 +3744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
@@ -3537,7 +3758,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="33" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3556,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3567,10 +3788,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3578,10 +3799,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3592,11 +3813,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="43.875" style="1" bestFit="1" customWidth="1"/>
@@ -3631,7 +3852,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.5">
@@ -3639,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.5">
@@ -3684,7 +3905,7 @@
     </row>
     <row r="11" spans="1:2" ht="15">
       <c r="A11" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
@@ -3692,7 +3913,7 @@
     </row>
     <row r="12" spans="1:2" ht="15">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
@@ -3700,7 +3921,7 @@
     </row>
     <row r="13" spans="1:2" ht="16.5">
       <c r="A13" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>13</v>
@@ -3708,7 +3929,7 @@
     </row>
     <row r="14" spans="1:2" ht="16.5">
       <c r="A14" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>13</v>
@@ -3716,7 +3937,7 @@
     </row>
     <row r="15" spans="1:2" ht="15">
       <c r="A15" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
@@ -3724,7 +3945,7 @@
     </row>
     <row r="16" spans="1:2" ht="15">
       <c r="A16" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
@@ -3743,7 +3964,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15">
@@ -3751,7 +3972,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15">
@@ -3759,7 +3980,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15">
@@ -3767,7 +3988,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15">
@@ -3775,47 +3996,47 @@
         <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15">
       <c r="A23" s="5" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15">
       <c r="A24" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15">
       <c r="A25" s="5" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15">
       <c r="A26" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15">
       <c r="A27" s="5" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15">
@@ -3823,44 +4044,44 @@
         <v>70</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15">
       <c r="A29" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="16.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15">
       <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="16.5">
+        <v>69</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15">
       <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="16.5">
+        <v>109</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15">
       <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>13</v>
+        <v>110</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16.5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B33" s="32" t="s">
         <v>13</v>
@@ -3868,7 +4089,7 @@
     </row>
     <row r="34" spans="1:2" ht="16.5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>13</v>
@@ -3876,39 +4097,39 @@
     </row>
     <row r="35" spans="1:2" ht="16.5">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15">
+    <row r="36" spans="1:2" ht="16.5">
       <c r="A36" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15">
+        <v>40</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="16.5">
       <c r="A37" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15">
+        <v>41</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="16.5">
       <c r="A38" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>9</v>
+        <v>42</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15">
       <c r="A39" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
@@ -3916,34 +4137,58 @@
     </row>
     <row r="40" spans="1:2" ht="15">
       <c r="A40" s="5" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15">
       <c r="A41" s="5" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15">
       <c r="A42" s="5" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15">
       <c r="A43" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15">
+      <c r="A44" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15">
+      <c r="A45" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15">
+      <c r="A46" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
